--- a/outputs/daily/hr_rankings_2026-06-27_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-27_full.xlsx
@@ -1102,34 +1102,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1386,34 +1382,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4442,34 +4434,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4726,34 +4714,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6966,34 +6950,30 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8296,7 +8276,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -13106,34 +13086,30 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19136,7 +19112,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -19696,7 +19672,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -19976,7 +19952,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -22542,34 +22518,30 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23588,7 +23560,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -27748,7 +27720,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28370,34 +28342,30 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -29210,34 +29178,30 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -29708,7 +29672,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -32488,7 +32452,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -34226,34 +34190,30 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -35614,34 +35574,30 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -35832,7 +35788,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36664,7 +36620,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -38876,7 +38832,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -40260,7 +40216,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -42818,34 +42774,30 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48106,34 +48058,30 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48390,34 +48338,30 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -49164,7 +49108,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -50062,34 +50006,30 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52216,7 +52156,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -55828,7 +55768,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -57566,34 +57506,30 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB206" t="inlineStr"/>
       <c r="AC206" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58402,34 +58338,30 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -63048,7 +62980,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -65820,7 +65752,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -70316,28 +70248,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W252" t="inlineStr"/>
-      <c r="X252" t="inlineStr"/>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y252" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB252" t="inlineStr"/>
       <c r="AC252" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70804,7 +70740,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -73960,34 +73896,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74244,34 +74176,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77300,34 +77228,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77584,34 +77508,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
